--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3263,7 +3263,7 @@
         <v>129114100</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>129123491</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129123490</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>129123489</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,6 +3436,8 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -3502,7 +3504,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, som bedöms vara max 10 år gamla på en gran i gammal granskog med minst hälften livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, som bedöms vara max 10 år gamla på en gran i gammal granskog. Minst medelhögt livsmiljövärde för tretåig hackspett baserat på volym stående död ved främst av gran på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>129114328</v>
       </c>
       <c r="B25" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112919</v>
+        <v>129123497</v>
       </c>
       <c r="B2" t="n">
-        <v>92508</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500446</v>
+        <v>500270</v>
       </c>
       <c r="R2" t="n">
-        <v>7005103</v>
+        <v>7005056</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,74 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112558</v>
+        <v>129123498</v>
       </c>
       <c r="B3" t="n">
-        <v>103252</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500373</v>
+        <v>500231</v>
       </c>
       <c r="R3" t="n">
-        <v>7005004</v>
+        <v>7005057</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,69 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129113904</v>
+        <v>129123522</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500645</v>
+        <v>500489</v>
       </c>
       <c r="R4" t="n">
-        <v>7005223</v>
+        <v>7005042</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,96 +950,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115554</v>
+        <v>129123478</v>
       </c>
       <c r="B5" t="n">
-        <v>100916</v>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500808</v>
+        <v>500526</v>
       </c>
       <c r="R5" t="n">
-        <v>7005138</v>
+        <v>7005046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,21 +1034,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1112,88 +1047,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129113196</v>
+        <v>129123485</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500611</v>
+        <v>500881</v>
       </c>
       <c r="R6" t="n">
-        <v>7005141</v>
+        <v>7005150</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,26 +1131,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor och 1 fröställnng inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1248,74 +1144,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129117273</v>
+        <v>129123486</v>
       </c>
       <c r="B7" t="n">
-        <v>92508</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500819</v>
+        <v>500231</v>
       </c>
       <c r="R7" t="n">
-        <v>7005148</v>
+        <v>7005057</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,21 +1228,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1365,74 +1241,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129117538</v>
+        <v>129123480</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500800</v>
+        <v>500771</v>
       </c>
       <c r="R8" t="n">
-        <v>7005156</v>
+        <v>7005191</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,21 +1325,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1482,31 +1338,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113282</v>
+        <v>129123515</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,53 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500628</v>
+        <v>500587</v>
       </c>
       <c r="R9" t="n">
-        <v>7005152</v>
+        <v>7005236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,11 +1427,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 52 plantor inom ca 1,5 m2 yta i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1608,31 +1435,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115608</v>
+        <v>129123488</v>
       </c>
       <c r="B10" t="n">
-        <v>92508</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,42 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500818</v>
+        <v>500537</v>
       </c>
       <c r="R10" t="n">
-        <v>7005140</v>
+        <v>7005233</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,21 +1519,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1725,31 +1532,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129112589</v>
+        <v>129112409</v>
       </c>
       <c r="B11" t="n">
-        <v>103252</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,27 +1559,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1786,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500419</v>
+        <v>500214</v>
       </c>
       <c r="R11" t="n">
-        <v>7005053</v>
+        <v>7005051</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129117456</v>
+        <v>129112919</v>
       </c>
       <c r="B12" t="n">
-        <v>100821</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,39 +1666,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500820</v>
+        <v>500446</v>
       </c>
       <c r="R12" t="n">
-        <v>7005146</v>
+        <v>7005103</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -1926,21 +1728,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1952,7 +1744,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1970,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129116986</v>
+        <v>129115608</v>
       </c>
       <c r="B13" t="n">
-        <v>100916</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,27 +1773,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2010,13 +1802,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501042</v>
+        <v>500818</v>
       </c>
       <c r="R13" t="n">
-        <v>7005204</v>
+        <v>7005140</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2045,7 +1837,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +1847,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +1861,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2087,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129112584</v>
+        <v>129115774</v>
       </c>
       <c r="B14" t="n">
-        <v>100916</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,42 +1890,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500406</v>
+        <v>500844</v>
       </c>
       <c r="R14" t="n">
-        <v>7005055</v>
+        <v>7005178</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2160,9 +1952,19 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129112623</v>
+        <v>129116791</v>
       </c>
       <c r="B15" t="n">
-        <v>103252</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,42 +2007,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500369</v>
+        <v>501009</v>
       </c>
       <c r="R15" t="n">
-        <v>7005085</v>
+        <v>7005189</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,9 +2069,19 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,52 +2113,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129114882</v>
+        <v>129116937</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2355,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500681</v>
+        <v>501029</v>
       </c>
       <c r="R16" t="n">
-        <v>7005153</v>
+        <v>7005173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2188,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2198,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 35 plantor och 1 överblommad blomställning inom ca 2 x 1 m2 yta i gammal barrblandskog.</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,7 +2212,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2440,7 +2233,7 @@
         <v>129117056</v>
       </c>
       <c r="B17" t="n">
-        <v>92508</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2554,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129112486</v>
+        <v>129117273</v>
       </c>
       <c r="B18" t="n">
-        <v>100916</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,42 +2358,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500276</v>
+        <v>500819</v>
       </c>
       <c r="R18" t="n">
-        <v>7005069</v>
+        <v>7005148</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,9 +2420,19 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,63 +2464,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129114612</v>
+        <v>129123494</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500664</v>
+        <v>500225</v>
       </c>
       <c r="R19" t="n">
-        <v>7005170</v>
+        <v>7005077</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2744,26 +2532,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2772,31 +2545,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129112447</v>
+        <v>129123495</v>
       </c>
       <c r="B20" t="n">
-        <v>103252</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,42 +2572,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500200</v>
+        <v>500860</v>
       </c>
       <c r="R20" t="n">
-        <v>7005064</v>
+        <v>7005176</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,74 +2642,64 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129112360</v>
+        <v>129113904</v>
       </c>
       <c r="B21" t="n">
-        <v>100916</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500225</v>
+        <v>500645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005061</v>
+        <v>7005223</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,7 +2742,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3007,53 +2780,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129118055</v>
+        <v>129114741</v>
       </c>
       <c r="B22" t="n">
-        <v>103252</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500422</v>
+        <v>500675</v>
       </c>
       <c r="R22" t="n">
-        <v>7005030</v>
+        <v>7005154</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3082,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +2860,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,7 +2879,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3124,67 +2917,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115715</v>
+        <v>129123520</v>
       </c>
       <c r="B23" t="n">
-        <v>104198</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500820</v>
+        <v>500366</v>
       </c>
       <c r="R23" t="n">
-        <v>7005164</v>
+        <v>7005037</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3211,26 +2985,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 5 buskplantor med ca 0,5 meters höjd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3239,79 +2998,64 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129114100</v>
+        <v>129123521</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Kyrkås, Brynjebodarna, Kyrkås, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500646</v>
+        <v>500497</v>
       </c>
       <c r="R24" t="n">
-        <v>7005179</v>
+        <v>7005205</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3338,26 +3082,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på ca 5 meters höjd på en tall.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3366,51 +3095,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129114328</v>
+        <v>129123483</v>
       </c>
       <c r="B25" t="n">
-        <v>57880</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3418,49 +3122,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Kyrkås, Brynjebodarna, Kyrkås, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500631</v>
+        <v>500656</v>
       </c>
       <c r="R25" t="n">
-        <v>7005153</v>
+        <v>7005205</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3487,26 +3179,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, som bedöms vara max 10 år gamla på en gran i gammal granskog. Minst medelhögt livsmiljövärde för tretåig hackspett baserat på volym stående död ved främst av gran på/kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3515,94 +3192,64 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129116791</v>
+        <v>129123499</v>
       </c>
       <c r="B26" t="n">
-        <v>92508</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501009</v>
+        <v>500562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005189</v>
+        <v>7005065</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3629,21 +3276,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3652,71 +3289,61 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129116888</v>
+        <v>129123500</v>
       </c>
       <c r="B27" t="n">
-        <v>100916</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501025</v>
+        <v>500685</v>
       </c>
       <c r="R27" t="n">
-        <v>7005180</v>
+        <v>7005192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,21 +3373,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3769,74 +3386,64 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129117890</v>
+        <v>129123501</v>
       </c>
       <c r="B28" t="n">
-        <v>100916</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500499</v>
+        <v>500493</v>
       </c>
       <c r="R28" t="n">
-        <v>7005061</v>
+        <v>7005210</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3863,21 +3470,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:16</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:16</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3886,31 +3483,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112409</v>
+        <v>129123496</v>
       </c>
       <c r="B29" t="n">
-        <v>92508</v>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3918,42 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500214</v>
+        <v>500553</v>
       </c>
       <c r="R29" t="n">
-        <v>7005051</v>
+        <v>7005069</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3993,74 +3580,74 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112874</v>
+        <v>129114100</v>
       </c>
       <c r="B30" t="n">
-        <v>103252</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Kyrkås, Brynjebodarna, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500438</v>
+        <v>500646</v>
       </c>
       <c r="R30" t="n">
-        <v>7005109</v>
+        <v>7005179</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4087,11 +3674,26 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på ca 5 meters höjd på en tall.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4104,6 +3706,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4121,38 +3743,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129116487</v>
+        <v>129114328</v>
       </c>
       <c r="B31" t="n">
-        <v>104198</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4162,17 +3786,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Kyrkås, Brynjebodarna, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500867</v>
+        <v>500631</v>
       </c>
       <c r="R31" t="n">
-        <v>7005174</v>
+        <v>7005153</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4201,7 +3825,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4211,12 +3835,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 ex av en ca 1 m hög tibast-buske.</t>
+          <t>Ringhack, äldre, som bedöms vara max 10 år gamla på en gran i gammal granskog. Minst medelhögt livsmiljövärde för tretåig hackspett baserat på volym stående död ved främst av gran på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4230,7 +3854,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4248,53 +3892,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129118014</v>
+        <v>129123489</v>
       </c>
       <c r="B32" t="n">
-        <v>100916</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500438</v>
+        <v>500852</v>
       </c>
       <c r="R32" t="n">
-        <v>7005035</v>
+        <v>7005148</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4321,19 +3960,14 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:20</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4344,74 +3978,72 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115774</v>
+        <v>129123490</v>
       </c>
       <c r="B33" t="n">
-        <v>92508</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500844</v>
+        <v>500604</v>
       </c>
       <c r="R33" t="n">
-        <v>7005178</v>
+        <v>7005224</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4438,19 +4070,14 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:59</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4461,74 +4088,64 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129112541</v>
+        <v>129123491</v>
       </c>
       <c r="B34" t="n">
-        <v>103252</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500344</v>
+        <v>500632</v>
       </c>
       <c r="R34" t="n">
-        <v>7005010</v>
+        <v>7005166</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,6 +4177,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4568,31 +4190,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129112851</v>
+        <v>129123516</v>
       </c>
       <c r="B35" t="n">
-        <v>100916</v>
+        <v>57945</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4600,42 +4217,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100110</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500441</v>
+        <v>500546</v>
       </c>
       <c r="R35" t="n">
-        <v>7005118</v>
+        <v>7005224</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4667,6 +4279,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4675,31 +4292,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129114741</v>
+        <v>129123493</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,37 +4319,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bodbäcken, Bodbäcken, Jmt</t>
+          <t>Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500675</v>
+        <v>500853</v>
       </c>
       <c r="R36" t="n">
-        <v>7005154</v>
+        <v>7005173</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4764,24 +4376,14 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,41 +4394,16 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4836,7 +4413,7 @@
         <v>129112387</v>
       </c>
       <c r="B37" t="n">
-        <v>99061</v>
+        <v>99456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,10 +4517,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115520</v>
+        <v>129113196</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4970,7 +4547,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4980,7 +4557,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4994,13 +4571,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500786</v>
+        <v>500611</v>
       </c>
       <c r="R38" t="n">
-        <v>7005140</v>
+        <v>7005141</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5029,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5039,12 +4616,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta i gammal flerskiktad barrblandskog.</t>
+          <t>Minst 22 plantor och 1 fröställnng inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5076,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129123509</v>
+        <v>129113282</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,17 +4681,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500549</v>
+        <v>500628</v>
       </c>
       <c r="R39" t="n">
-        <v>7005221</v>
+        <v>7005152</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5149,6 +4745,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 52 plantor inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5157,60 +4758,84 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129123517</v>
+        <v>129114612</v>
       </c>
       <c r="B40" t="n">
-        <v>91601</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500589</v>
+        <v>500664</v>
       </c>
       <c r="R40" t="n">
-        <v>7005191</v>
+        <v>7005170</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5237,11 +4862,26 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5250,61 +4890,85 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129123521</v>
+        <v>129114882</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500497</v>
+        <v>500681</v>
       </c>
       <c r="R41" t="n">
-        <v>7005205</v>
+        <v>7005153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5334,11 +4998,26 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 35 plantor och 1 överblommad blomställning inom ca 2 x 1 m2 yta i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5347,64 +5026,88 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129123480</v>
+        <v>129115520</v>
       </c>
       <c r="B42" t="n">
-        <v>91595</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500771</v>
+        <v>500786</v>
       </c>
       <c r="R42" t="n">
-        <v>7005191</v>
+        <v>7005140</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5431,11 +5134,26 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta i gammal flerskiktad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5444,48 +5162,53 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129123483</v>
+        <v>129123481</v>
       </c>
       <c r="B43" t="n">
-        <v>83039</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5495,10 +5218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500656</v>
+        <v>500711</v>
       </c>
       <c r="R43" t="n">
-        <v>7005205</v>
+        <v>7005171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5533,6 +5256,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 st</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5545,44 +5273,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129123495</v>
+        <v>129123482</v>
       </c>
       <c r="B44" t="n">
-        <v>92536</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5592,10 +5320,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500860</v>
+        <v>500666</v>
       </c>
       <c r="R44" t="n">
-        <v>7005176</v>
+        <v>7005126</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5630,6 +5358,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 st</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5642,22 +5375,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129123514</v>
+        <v>129123502</v>
       </c>
       <c r="B45" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5689,10 +5422,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500502</v>
+        <v>500586</v>
       </c>
       <c r="R45" t="n">
-        <v>7005186</v>
+        <v>7005153</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5729,7 +5462,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>14 st</t>
+          <t>41st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5744,44 +5477,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129123484</v>
+        <v>129123503</v>
       </c>
       <c r="B46" t="n">
-        <v>103281</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5791,10 +5524,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500400</v>
+        <v>500654</v>
       </c>
       <c r="R46" t="n">
-        <v>7005099</v>
+        <v>7005101</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5841,44 +5574,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129123500</v>
+        <v>129123504</v>
       </c>
       <c r="B47" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5888,10 +5621,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500685</v>
+        <v>500695</v>
       </c>
       <c r="R47" t="n">
-        <v>7005192</v>
+        <v>7005144</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5938,44 +5671,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129123515</v>
+        <v>129123505</v>
       </c>
       <c r="B48" t="n">
-        <v>91595</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5985,10 +5718,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500587</v>
+        <v>500704</v>
       </c>
       <c r="R48" t="n">
-        <v>7005236</v>
+        <v>7005182</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6035,44 +5768,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129123496</v>
+        <v>129123506</v>
       </c>
       <c r="B49" t="n">
-        <v>80204</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6082,10 +5815,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500553</v>
+        <v>500621</v>
       </c>
       <c r="R49" t="n">
-        <v>7005069</v>
+        <v>7005229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6120,6 +5853,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>10st</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6132,22 +5870,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129123508</v>
+        <v>129123507</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,10 +5917,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500576</v>
+        <v>500615</v>
       </c>
       <c r="R50" t="n">
-        <v>7005209</v>
+        <v>7005237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6219,7 +5957,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>11st</t>
+          <t>37st</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6234,22 +5972,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129123512</v>
+        <v>129123508</v>
       </c>
       <c r="B51" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6281,10 +6019,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500528</v>
+        <v>500576</v>
       </c>
       <c r="R51" t="n">
-        <v>7005189</v>
+        <v>7005209</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6319,6 +6057,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>11st</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6331,44 +6074,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129123494</v>
+        <v>129123509</v>
       </c>
       <c r="B52" t="n">
-        <v>92536</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6378,10 +6121,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500225</v>
+        <v>500549</v>
       </c>
       <c r="R52" t="n">
-        <v>7005077</v>
+        <v>7005221</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6428,44 +6171,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129123491</v>
+        <v>129123510</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6475,10 +6218,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500632</v>
+        <v>500552</v>
       </c>
       <c r="R53" t="n">
-        <v>7005166</v>
+        <v>7005194</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6515,7 +6258,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>41st</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6542,10 +6285,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129123482</v>
+        <v>129123511</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,10 +6320,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500666</v>
+        <v>500546</v>
       </c>
       <c r="R54" t="n">
-        <v>7005126</v>
+        <v>7005187</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,11 +6358,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>30 st</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6632,22 +6370,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129123502</v>
+        <v>129123512</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6679,10 +6417,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500586</v>
+        <v>500528</v>
       </c>
       <c r="R55" t="n">
-        <v>7005153</v>
+        <v>7005189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6717,11 +6455,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>41st</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6734,42 +6467,46 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129123519</v>
+        <v>129123513</v>
       </c>
       <c r="B56" t="n">
-        <v>91601</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6777,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500605</v>
+        <v>500503</v>
       </c>
       <c r="R56" t="n">
-        <v>7005223</v>
+        <v>7005210</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6827,22 +6564,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129123503</v>
+        <v>129123514</v>
       </c>
       <c r="B57" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6874,10 +6611,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500654</v>
+        <v>500502</v>
       </c>
       <c r="R57" t="n">
-        <v>7005101</v>
+        <v>7005186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6912,6 +6649,11 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>14 st</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6924,68 +6666,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129123490</v>
+        <v>129112447</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>103682</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500604</v>
+        <v>500200</v>
       </c>
       <c r="R58" t="n">
-        <v>7005224</v>
+        <v>7005064</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7017,11 +6756,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7030,60 +6764,74 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129123518</v>
+        <v>129112541</v>
       </c>
       <c r="B59" t="n">
-        <v>91601</v>
+        <v>103682</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>222002</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>500769</v>
+        <v>500344</v>
       </c>
       <c r="R59" t="n">
-        <v>7005124</v>
+        <v>7005010</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7123,64 +6871,74 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129123513</v>
+        <v>129112558</v>
       </c>
       <c r="B60" t="n">
-        <v>98756</v>
+        <v>103682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>500503</v>
+        <v>500373</v>
       </c>
       <c r="R60" t="n">
-        <v>7005210</v>
+        <v>7005004</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7220,61 +6978,71 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129123522</v>
+        <v>129112589</v>
       </c>
       <c r="B61" t="n">
-        <v>92272</v>
+        <v>103682</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>898</v>
+        <v>222002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>500489</v>
+        <v>500419</v>
       </c>
       <c r="R61" t="n">
-        <v>7005042</v>
+        <v>7005053</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7318,63 +7086,73 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129123489</v>
+        <v>129112623</v>
       </c>
       <c r="B62" t="n">
-        <v>57740</v>
+        <v>103682</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500852</v>
+        <v>500369</v>
       </c>
       <c r="R62" t="n">
-        <v>7005148</v>
+        <v>7005085</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7406,11 +7184,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7419,61 +7192,71 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129123499</v>
+        <v>129112874</v>
       </c>
       <c r="B63" t="n">
-        <v>80175</v>
+        <v>103682</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>222002</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500562</v>
+        <v>500438</v>
       </c>
       <c r="R63" t="n">
-        <v>7005065</v>
+        <v>7005109</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7517,63 +7300,73 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129123501</v>
+        <v>129118055</v>
       </c>
       <c r="B64" t="n">
-        <v>80175</v>
+        <v>103682</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222002</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500493</v>
+        <v>500422</v>
       </c>
       <c r="R64" t="n">
-        <v>7005210</v>
+        <v>7005030</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7600,11 +7393,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7613,64 +7416,74 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129123506</v>
+        <v>129118114</v>
       </c>
       <c r="B65" t="n">
-        <v>98756</v>
+        <v>103682</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>500621</v>
+        <v>500417</v>
       </c>
       <c r="R65" t="n">
-        <v>7005229</v>
+        <v>7004996</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7697,14 +7510,24 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>10st</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,48 +7538,53 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129123478</v>
+        <v>129123484</v>
       </c>
       <c r="B66" t="n">
-        <v>81055</v>
+        <v>103682</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>222002</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7766,10 +7594,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>500526</v>
+        <v>500400</v>
       </c>
       <c r="R66" t="n">
-        <v>7005046</v>
+        <v>7005099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7816,60 +7644,79 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129123485</v>
+        <v>129115715</v>
       </c>
       <c r="B67" t="n">
-        <v>91581</v>
+        <v>104627</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>500881</v>
+        <v>500820</v>
       </c>
       <c r="R67" t="n">
-        <v>7005150</v>
+        <v>7005164</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7896,11 +7743,26 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 5 buskplantor med ca 0,5 meters höjd.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7909,61 +7771,76 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129123493</v>
+        <v>129116487</v>
       </c>
       <c r="B68" t="n">
-        <v>57890</v>
+        <v>104627</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500853</v>
+        <v>500867</v>
       </c>
       <c r="R68" t="n">
-        <v>7005173</v>
+        <v>7005174</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7993,14 +7870,24 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>1 ex av en ca 1 m hög tibast-buske.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8011,26 +7898,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129123488</v>
+        <v>129116916</v>
       </c>
       <c r="B69" t="n">
-        <v>92299</v>
+        <v>104627</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8038,34 +7930,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>222412</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500537</v>
+        <v>501016</v>
       </c>
       <c r="R69" t="n">
-        <v>7005233</v>
+        <v>7005168</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8095,11 +7992,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8108,64 +8015,74 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129123498</v>
+        <v>129112360</v>
       </c>
       <c r="B70" t="n">
-        <v>91879</v>
+        <v>101325</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500231</v>
+        <v>500225</v>
       </c>
       <c r="R70" t="n">
-        <v>7005057</v>
+        <v>7005061</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8205,64 +8122,74 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129123507</v>
+        <v>129112486</v>
       </c>
       <c r="B71" t="n">
-        <v>98756</v>
+        <v>101325</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500615</v>
+        <v>500276</v>
       </c>
       <c r="R71" t="n">
-        <v>7005237</v>
+        <v>7005069</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8294,11 +8221,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>37st</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8307,26 +8229,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129123516</v>
+        <v>129112584</v>
       </c>
       <c r="B72" t="n">
-        <v>57722</v>
+        <v>101325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8334,34 +8261,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100110</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500546</v>
+        <v>500406</v>
       </c>
       <c r="R72" t="n">
-        <v>7005224</v>
+        <v>7005055</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8396,11 +8328,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Hane</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8409,64 +8336,74 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129123486</v>
+        <v>129112851</v>
       </c>
       <c r="B73" t="n">
-        <v>91581</v>
+        <v>101325</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500231</v>
+        <v>500441</v>
       </c>
       <c r="R73" t="n">
-        <v>7005057</v>
+        <v>7005118</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8506,61 +8443,76 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129123520</v>
+        <v>129115554</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>101325</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500366</v>
+        <v>500808</v>
       </c>
       <c r="R74" t="n">
-        <v>7005037</v>
+        <v>7005138</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8590,11 +8542,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8603,61 +8565,71 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129123510</v>
+        <v>129116888</v>
       </c>
       <c r="B75" t="n">
-        <v>98756</v>
+        <v>101325</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500552</v>
+        <v>501025</v>
       </c>
       <c r="R75" t="n">
-        <v>7005194</v>
+        <v>7005180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8687,14 +8659,19 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>41st</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8705,64 +8682,74 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129123504</v>
+        <v>129116986</v>
       </c>
       <c r="B76" t="n">
-        <v>98756</v>
+        <v>101325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>500695</v>
+        <v>501042</v>
       </c>
       <c r="R76" t="n">
-        <v>7005144</v>
+        <v>7005204</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8789,11 +8776,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8802,64 +8799,74 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129123481</v>
+        <v>129117538</v>
       </c>
       <c r="B77" t="n">
-        <v>98756</v>
+        <v>101325</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>500711</v>
+        <v>500800</v>
       </c>
       <c r="R77" t="n">
-        <v>7005171</v>
+        <v>7005156</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8886,14 +8893,19 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>20 st</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8904,64 +8916,74 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129123505</v>
+        <v>129117890</v>
       </c>
       <c r="B78" t="n">
-        <v>98756</v>
+        <v>101325</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>500704</v>
+        <v>500499</v>
       </c>
       <c r="R78" t="n">
-        <v>7005182</v>
+        <v>7005061</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,11 +9010,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9001,64 +9033,74 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129123497</v>
+        <v>129118014</v>
       </c>
       <c r="B79" t="n">
-        <v>91532</v>
+        <v>101325</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Brynjebodarna, Brynjebodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>500270</v>
+        <v>500438</v>
       </c>
       <c r="R79" t="n">
-        <v>7005056</v>
+        <v>7005035</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9085,11 +9127,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9098,64 +9150,74 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129123511</v>
+        <v>129117456</v>
       </c>
       <c r="B80" t="n">
-        <v>98756</v>
+        <v>101227</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Brynjebodarna, Jmt</t>
+          <t>Bodbäcken, Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>500546</v>
+        <v>500820</v>
       </c>
       <c r="R80" t="n">
-        <v>7005187</v>
+        <v>7005146</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9182,11 +9244,21 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9195,16 +9267,21 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 58266-2025 artfynd.xlsx
+++ b/artfynd/A 58266-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123478</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123485</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123480</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123515</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123488</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112409</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115608</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116791</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116937</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117056</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2675,6 +2770,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117273</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123494</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2869,6 +2974,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123495</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2991,6 +3101,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3128,6 +3243,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114741</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3225,6 +3345,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123520</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3322,6 +3447,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123521</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123483</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3516,6 +3651,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123499</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123500</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3710,6 +3855,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123501</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3807,6 +3957,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123496</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3954,6 +4109,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4103,6 +4263,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114328</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123489</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123490</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123491</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4519,6 +4699,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123516</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4621,6 +4806,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123493</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4757,6 +4947,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113196</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4883,6 +5078,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113282</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5015,6 +5215,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5151,6 +5356,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114882</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5287,6 +5497,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115520</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5389,6 +5604,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123481</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5491,6 +5711,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123482</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5593,6 +5818,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123502</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5690,6 +5920,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123503</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5787,6 +6022,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123504</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5884,6 +6124,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123505</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5986,6 +6231,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123506</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6088,6 +6338,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123507</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6190,6 +6445,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123508</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6287,6 +6547,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123509</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6389,6 +6654,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123510</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6486,6 +6756,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123511</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6583,6 +6858,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123512</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6680,6 +6960,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123513</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6782,6 +7067,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123514</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6889,6 +7179,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112541</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6996,6 +7291,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112558</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7103,6 +7403,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112589</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7210,6 +7515,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112623</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7317,6 +7627,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112874</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7434,6 +7749,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7556,6 +7876,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118114</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7653,6 +7978,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123484</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7789,6 +8119,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115715</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7916,6 +8251,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116487</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8033,6 +8373,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116916</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8140,6 +8485,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112360</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8247,6 +8597,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112486</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8354,6 +8709,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112584</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8461,6 +8821,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112851</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8583,6 +8948,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115554</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8700,6 +9070,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116888</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8817,6 +9192,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116986</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8934,6 +9314,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117538</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9051,6 +9436,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117890</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9168,6 +9558,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118014</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9285,8 +9680,94 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>